--- a/data/gravel/BMC URS 2024.xlsx
+++ b/data/gravel/BMC URS 2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8B597A-22E8-5B4F-ABF0-813704B1C392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B04501-DF24-B74D-929E-982C49D61A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="1100" windowWidth="28040" windowHeight="14560" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="28040" windowHeight="14560" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
   </bookViews>
   <sheets>
     <sheet name="BMC URS 2024" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="139">
   <si>
     <t>brand</t>
   </si>
@@ -59,12 +59,6 @@
     <t>carbon</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -344,10 +338,121 @@
     <t>stem_angle</t>
   </si>
   <si>
-    <t>a10:g38</t>
-  </si>
-  <si>
-    <t>https://us.bmc-switzerland.com/collections/urs-gravel-bikes/products/urs-one-bikes-bmc-26a-000042#geometry_4FHfYA</t>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>ASTM 2</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
+  </si>
+  <si>
+    <t>https://us.bmc-switzerland.com/pages/platform/platform-urs</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>a10:g39</t>
+  </si>
+  <si>
+    <t>PF86</t>
+  </si>
+  <si>
+    <t>700c width max</t>
   </si>
 </sst>
 </file>
@@ -357,7 +462,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -399,6 +504,12 @@
       <color rgb="FF353535"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -420,7 +531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -432,6 +543,10 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -766,34 +881,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299AF885-3999-4E4F-8F92-5857EF0F7F08}">
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:AH43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" style="1" customWidth="1"/>
-    <col min="3" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="1"/>
-    <col min="10" max="24" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="1"/>
+    <col min="11" max="25" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -801,7 +919,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -809,92 +927,232 @@
         <v>45853</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="G6" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y6" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z6" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB6" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC6" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD6" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH6" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>47</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1">
+        <v>1</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>180</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>3649</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" ht="22" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="22" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="F10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="J10" s="10" t="s">
+      <c r="H10" s="4"/>
+      <c r="I10" s="3"/>
+      <c r="K10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:34" ht="22" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5">
         <v>390</v>
@@ -911,33 +1169,34 @@
       <c r="G11" s="5">
         <v>430</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="J11" s="7">
+      <c r="H11" s="5"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="7">
         <v>538</v>
       </c>
-      <c r="K11" s="7">
+      <c r="L11" s="7">
         <v>569</v>
       </c>
-      <c r="L11" s="7">
+      <c r="M11" s="7">
         <v>603</v>
       </c>
-      <c r="M11" s="7">
+      <c r="N11" s="7">
         <v>641</v>
       </c>
-      <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" ht="22" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" s="5">
         <v>560</v>
@@ -954,33 +1213,34 @@
       <c r="G12" s="5">
         <v>640</v>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="J12" s="7">
+      <c r="H12" s="5"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K12" s="7">
         <v>403</v>
       </c>
-      <c r="K12" s="7">
+      <c r="L12" s="7">
         <v>415</v>
       </c>
-      <c r="L12" s="7">
+      <c r="M12" s="7">
         <v>419</v>
       </c>
-      <c r="M12" s="7">
+      <c r="N12" s="7">
         <v>429</v>
       </c>
-      <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:34" ht="22" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" s="5">
         <v>115</v>
@@ -997,33 +1257,34 @@
       <c r="G13" s="5">
         <v>115</v>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="J13" s="7">
+      <c r="H13" s="5"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K13" s="7">
         <v>431</v>
       </c>
-      <c r="K13" s="7">
+      <c r="L13" s="7">
         <v>459</v>
       </c>
-      <c r="L13" s="7">
+      <c r="M13" s="7">
         <v>492</v>
       </c>
-      <c r="M13" s="7">
+      <c r="N13" s="7">
         <v>527</v>
       </c>
-      <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:34" ht="22" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="5">
         <v>70</v>
@@ -1040,33 +1301,34 @@
       <c r="G14" s="5">
         <v>70</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14" s="7">
+      <c r="H14" s="5"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" s="7">
         <v>557</v>
       </c>
-      <c r="K14" s="7">
+      <c r="L14" s="7">
         <v>578</v>
       </c>
-      <c r="L14" s="7">
+      <c r="M14" s="7">
         <v>591</v>
       </c>
-      <c r="M14" s="7">
+      <c r="N14" s="7">
         <v>612</v>
       </c>
-      <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:34" ht="22" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C15" s="5">
         <v>76</v>
@@ -1083,33 +1345,34 @@
       <c r="G15" s="5">
         <v>76</v>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="J15" s="7">
+      <c r="H15" s="5"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="7">
         <v>113</v>
       </c>
-      <c r="K15" s="7">
+      <c r="L15" s="7">
         <v>146</v>
       </c>
-      <c r="L15" s="7">
+      <c r="M15" s="7">
         <v>172</v>
       </c>
-      <c r="M15" s="7">
+      <c r="N15" s="7">
         <v>207</v>
       </c>
-      <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:34" ht="22" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" s="5">
         <v>170</v>
@@ -1126,12 +1389,10 @@
       <c r="G16" s="5">
         <v>175</v>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" s="7">
-        <v>74</v>
+      <c r="H16" s="5"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="K16" s="7">
         <v>74</v>
@@ -1142,17 +1403,20 @@
       <c r="M16" s="7">
         <v>74</v>
       </c>
-      <c r="N16" s="3"/>
+      <c r="N16" s="7">
+        <v>74</v>
+      </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" s="5">
         <v>405</v>
@@ -1169,11 +1433,9 @@
       <c r="G17" s="5">
         <v>415</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="J17" s="7">
-        <v>70</v>
+      <c r="H17" s="5"/>
+      <c r="J17" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="K17" s="7">
         <v>70</v>
@@ -1184,17 +1446,20 @@
       <c r="M17" s="7">
         <v>70</v>
       </c>
-      <c r="N17" s="3"/>
+      <c r="N17" s="7">
+        <v>70</v>
+      </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" s="5">
         <v>50</v>
@@ -1211,11 +1476,9 @@
       <c r="G18" s="5">
         <v>45</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18" s="7">
-        <v>425</v>
+      <c r="H18" s="5"/>
+      <c r="J18" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="K18" s="7">
         <v>425</v>
@@ -1226,17 +1489,20 @@
       <c r="M18" s="7">
         <v>425</v>
       </c>
-      <c r="N18" s="3"/>
+      <c r="N18" s="7">
+        <v>425</v>
+      </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C19" s="5">
         <v>633</v>
@@ -1253,32 +1519,33 @@
       <c r="G19" s="5">
         <v>693</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J19" s="7">
+      <c r="H19" s="5"/>
+      <c r="J19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="7">
         <v>625</v>
       </c>
-      <c r="K19" s="7">
+      <c r="L19" s="7">
         <v>648</v>
       </c>
-      <c r="L19" s="7">
+      <c r="M19" s="7">
         <v>665</v>
       </c>
-      <c r="M19" s="7">
+      <c r="N19" s="7">
         <v>700</v>
       </c>
-      <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C20" s="5">
         <v>133</v>
@@ -1295,32 +1562,33 @@
       <c r="G20" s="5">
         <v>204</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J20" s="7">
+      <c r="H20" s="5"/>
+      <c r="J20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="7">
         <v>1041</v>
       </c>
-      <c r="K20" s="7">
+      <c r="L20" s="7">
         <v>1064</v>
       </c>
-      <c r="L20" s="7">
+      <c r="M20" s="7">
         <v>1081</v>
       </c>
-      <c r="M20" s="7">
+      <c r="N20" s="7">
         <v>1105</v>
       </c>
-      <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C21" s="5">
         <v>69</v>
@@ -1337,11 +1605,9 @@
       <c r="G21" s="5">
         <v>69.5</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="J21" s="7">
-        <v>69</v>
+      <c r="H21" s="5"/>
+      <c r="J21" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="K21" s="7">
         <v>69</v>
@@ -1352,17 +1618,20 @@
       <c r="M21" s="7">
         <v>69</v>
       </c>
-      <c r="N21" s="3"/>
+      <c r="N21" s="7">
+        <v>69</v>
+      </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C22" s="5">
         <v>430</v>
@@ -1379,11 +1648,9 @@
       <c r="G22" s="5">
         <v>430</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="J22" s="7">
-        <v>407</v>
+      <c r="H22" s="5"/>
+      <c r="J22" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="K22" s="7">
         <v>407</v>
@@ -1394,17 +1661,20 @@
       <c r="M22" s="7">
         <v>407</v>
       </c>
-      <c r="N22" s="3"/>
+      <c r="N22" s="7">
+        <v>407</v>
+      </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C23" s="5">
         <v>74.5</v>
@@ -1421,11 +1691,9 @@
       <c r="G23" s="5">
         <v>74.5</v>
       </c>
-      <c r="I23" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J23" s="7">
-        <v>45</v>
+      <c r="H23" s="5"/>
+      <c r="J23" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="K23" s="7">
         <v>45</v>
@@ -1436,17 +1704,20 @@
       <c r="M23" s="7">
         <v>45</v>
       </c>
-      <c r="N23" s="3"/>
+      <c r="N23" s="7">
+        <v>45</v>
+      </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C24" s="5">
         <v>430</v>
@@ -1463,11 +1734,9 @@
       <c r="G24" s="5">
         <v>540</v>
       </c>
-      <c r="I24" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="J24" s="7">
-        <v>77</v>
+      <c r="H24" s="5"/>
+      <c r="J24" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="K24" s="7">
         <v>77</v>
@@ -1478,13 +1747,16 @@
       <c r="M24" s="7">
         <v>77</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="N24" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C25" s="5">
         <v>310</v>
@@ -1501,32 +1773,33 @@
       <c r="G25" s="5">
         <v>360</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J25" s="8">
+      <c r="H25" s="5"/>
+      <c r="J25" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="K25" s="8">
         <v>170</v>
-      </c>
-      <c r="K25" s="8">
-        <v>172.5</v>
       </c>
       <c r="L25" s="8">
         <v>172.5</v>
       </c>
       <c r="M25" s="8">
+        <v>172.5</v>
+      </c>
+      <c r="N25" s="8">
         <v>175</v>
       </c>
-      <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C26" s="5">
         <v>0</v>
@@ -1543,32 +1816,33 @@
       <c r="G26" s="5">
         <v>0</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="J26" s="7">
-        <v>70</v>
+      <c r="H26" s="5"/>
+      <c r="J26" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="K26" s="7">
         <v>70</v>
       </c>
       <c r="L26" s="7">
+        <v>70</v>
+      </c>
+      <c r="M26" s="7">
         <v>80</v>
       </c>
-      <c r="M26" s="7">
+      <c r="N26" s="7">
         <v>90</v>
       </c>
-      <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" s="5">
         <v>727</v>
@@ -1585,29 +1859,30 @@
       <c r="G27" s="5">
         <v>795</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J27" s="7">
-        <v>420</v>
+      <c r="H27" s="5"/>
+      <c r="J27" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="K27" s="7">
         <v>420</v>
       </c>
       <c r="L27" s="7">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="M27" s="7">
         <v>440</v>
       </c>
-      <c r="N27" s="3"/>
+      <c r="N27" s="7">
+        <v>440</v>
+      </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1615,11 +1890,9 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
-      <c r="I28" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="J28" s="7">
-        <v>120</v>
+      <c r="H28" s="5"/>
+      <c r="J28" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="K28" s="7">
         <v>120</v>
@@ -1630,13 +1903,16 @@
       <c r="M28" s="7">
         <v>120</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="N28" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C29" s="5">
         <v>-8</v>
@@ -1653,11 +1929,9 @@
       <c r="G29" s="5">
         <v>-8</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="J29" s="7">
-        <v>80</v>
+      <c r="H29" s="5"/>
+      <c r="J29" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="K29" s="7">
         <v>80</v>
@@ -1668,13 +1942,16 @@
       <c r="M29" s="7">
         <v>80</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="N29" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C30" s="5">
         <v>70</v>
@@ -1691,28 +1968,29 @@
       <c r="G30" s="5">
         <v>90</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="J30" s="7">
+      <c r="H30" s="5"/>
+      <c r="J30" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K30" s="7">
         <v>748</v>
       </c>
-      <c r="K30" s="7">
+      <c r="L30" s="7">
         <v>778</v>
       </c>
-      <c r="L30" s="7">
+      <c r="M30" s="7">
         <v>810</v>
       </c>
-      <c r="M30" s="7">
+      <c r="N30" s="7">
         <v>846</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C31" s="5">
         <v>545</v>
@@ -1729,28 +2007,29 @@
       <c r="G31" s="5">
         <v>607</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="J31" s="7">
+      <c r="H31" s="5"/>
+      <c r="J31" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K31" s="7">
         <v>330</v>
       </c>
-      <c r="K31" s="7">
+      <c r="L31" s="7">
         <v>380</v>
-      </c>
-      <c r="L31" s="7">
-        <v>430</v>
       </c>
       <c r="M31" s="7">
         <v>430</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" ht="22" x14ac:dyDescent="0.3">
+      <c r="N31" s="7">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="22" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C32" s="5">
         <v>84</v>
@@ -1767,11 +2046,9 @@
       <c r="G32" s="5">
         <v>86</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="9">
-        <v>700</v>
+      <c r="H32" s="5"/>
+      <c r="J32" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="K32" s="9">
         <v>700</v>
@@ -1782,13 +2059,16 @@
       <c r="M32" s="9">
         <v>700</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" ht="22" x14ac:dyDescent="0.3">
+      <c r="N32" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="22" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C33" s="5">
         <v>1052</v>
@@ -1805,11 +2085,9 @@
       <c r="G33" s="5">
         <v>1112</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J33" s="9">
-        <v>40</v>
+      <c r="H33" s="5"/>
+      <c r="J33" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="K33" s="9">
         <v>40</v>
@@ -1820,31 +2098,22 @@
       <c r="M33" s="9">
         <v>40</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N33" s="9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="22" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="J34" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C34" s="1">
-        <v>700</v>
-      </c>
-      <c r="D34" s="1">
-        <v>700</v>
-      </c>
-      <c r="E34" s="1">
-        <v>700</v>
-      </c>
-      <c r="F34" s="1">
-        <v>700</v>
-      </c>
-      <c r="G34" s="1">
-        <v>700</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J34" s="9">
-        <v>42</v>
       </c>
       <c r="K34" s="9">
         <v>42</v>
@@ -1855,169 +2124,194 @@
       <c r="M34" s="9">
         <v>42</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N34" s="9">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="1">
+        <v>700</v>
+      </c>
+      <c r="D35" s="1">
+        <v>700</v>
+      </c>
+      <c r="E35" s="1">
+        <v>700</v>
+      </c>
+      <c r="F35" s="1">
+        <v>700</v>
+      </c>
+      <c r="G35" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="1">
+        <v>44</v>
+      </c>
+      <c r="D36" s="1">
+        <v>44</v>
+      </c>
+      <c r="E36" s="1">
+        <v>44</v>
+      </c>
+      <c r="F36" s="1">
+        <v>44</v>
+      </c>
+      <c r="G36" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="1">
+        <v>47</v>
+      </c>
+      <c r="D37" s="1">
+        <v>47</v>
+      </c>
+      <c r="E37" s="1">
+        <v>47</v>
+      </c>
+      <c r="F37" s="1">
+        <v>47</v>
+      </c>
+      <c r="G37" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="1">
-        <v>44</v>
-      </c>
-      <c r="D35" s="1">
-        <v>44</v>
-      </c>
-      <c r="E35" s="1">
-        <v>44</v>
-      </c>
-      <c r="F35" s="1">
-        <v>44</v>
-      </c>
-      <c r="G35" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="1">
-        <v>47</v>
-      </c>
-      <c r="D36" s="1">
-        <v>47</v>
-      </c>
-      <c r="E36" s="1">
-        <v>47</v>
-      </c>
-      <c r="F36" s="1">
-        <v>47</v>
-      </c>
-      <c r="G36" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="1">
-        <f>C39</f>
+      <c r="C38" s="1">
+        <f>C40</f>
         <v>160</v>
       </c>
-      <c r="D37" s="1">
-        <f>AVERAGE(D39,C40)</f>
+      <c r="D38" s="1">
+        <f>AVERAGE(D40,C41)</f>
         <v>166</v>
       </c>
-      <c r="E37" s="1">
-        <f t="shared" ref="E37:G37" si="0">AVERAGE(E39,D40)</f>
+      <c r="E38" s="1">
+        <f t="shared" ref="E38:F38" si="0">AVERAGE(E40,D41)</f>
         <v>169</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F38" s="1">
         <f t="shared" si="0"/>
         <v>177</v>
       </c>
-      <c r="G37" s="1">
-        <f t="shared" si="0"/>
+      <c r="G38" s="1">
+        <f>AVERAGE(G40,F41)</f>
         <v>188</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="1">
-        <f>D37</f>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="1">
+        <f>D38</f>
         <v>166</v>
       </c>
-      <c r="D38" s="1">
-        <f t="shared" ref="D38:F38" si="1">E37</f>
+      <c r="D39" s="1">
+        <f t="shared" ref="D39:E39" si="1">E38</f>
         <v>169</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E39" s="1">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
-      <c r="F38" s="1">
-        <f t="shared" si="1"/>
+      <c r="F39" s="1">
+        <f>G38</f>
         <v>188</v>
       </c>
-      <c r="G38" s="1">
-        <f t="shared" ref="G38" si="2">G40</f>
+      <c r="G39" s="1">
+        <f t="shared" ref="G39" si="2">G41</f>
         <v>200</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="1">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C40" s="1">
         <v>160</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D40" s="1">
         <v>165</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E40" s="1">
         <v>168</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F40" s="1">
         <v>176</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G40" s="1">
         <v>188</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C40" s="1">
+    <row r="41" spans="1:14" ht="22" x14ac:dyDescent="0.3">
+      <c r="C41" s="1">
         <v>167</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D41" s="1">
         <v>170</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E41" s="1">
         <v>178</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F41" s="1">
         <v>188</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G41" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" ht="22" x14ac:dyDescent="0.3">
-      <c r="B41" s="5" t="s">
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="1:14" ht="22" x14ac:dyDescent="0.3">
+      <c r="B42" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="E42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="F42" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="G42" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="22" x14ac:dyDescent="0.3">
-      <c r="B42" s="5" t="s">
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="1:14" ht="22" x14ac:dyDescent="0.3">
+      <c r="B43" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="E43" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>54</v>
+      <c r="G43" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/BMC URS 2024.xlsx
+++ b/data/gravel/BMC URS 2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B04501-DF24-B74D-929E-982C49D61A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C436570B-1D26-A24D-B133-FFA5B57510FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="860" windowWidth="28040" windowHeight="14560" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="140">
   <si>
     <t>brand</t>
   </si>
@@ -453,6 +453,9 @@
   </si>
   <si>
     <t>700c width max</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -1055,6 +1058,9 @@
       <c r="P7" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="Q7" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="T7" s="1" t="s">
         <v>137</v>
       </c>
